--- a/education_surveys/032_mid_semester_course_evaluation_form--education_surveys.xlsx
+++ b/education_surveys/032_mid_semester_course_evaluation_form--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1796,8 +1796,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'engaged'}</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Engaged'}</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disengaged'}</t>
+          <t>disengaged</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disengaged'}</t>
+          <t>Disengaged</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_engaged'}</t>
+          <t>somewhat_engaged</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Engaged'}</t>
+          <t>Somewhat Engaged</t>
         </is>
       </c>
     </row>
